--- a/docs/StructureDefinition-VitalSignsObservationBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationBP.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3877" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1669,183 +1669,11 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">vs-3
 </t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>667: transform using Split_rate_value.Diastolic on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
-  </si>
-  <si>
-    <t>Vital.VitalSign.Diastolic
-Vital.VitalSign.Systolic
-Vital.VitalSign.VitalResult
-Vital.VitalSign.VitalResultNumeric</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -1912,31 +1740,172 @@
     <t>Observation.component:systolic.value[x]</t>
   </si>
   <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].id</t>
   </si>
   <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].extension</t>
   </si>
   <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].value</t>
   </si>
   <si>
+    <t>Observation.component.value[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>666: transform using Split_rate_value.Systolic on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.Diastolic
+Vital.VitalSign.Systolic
+Vital.VitalSign.VitalResult
+Vital.VitalSign.VitalResultNumeric</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].comparator</t>
   </si>
   <si>
+    <t>Observation.component.value[x].comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].unit</t>
   </si>
   <si>
+    <t>Observation.component.value[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].system</t>
   </si>
   <si>
+    <t>Observation.component.value[x].system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
     <t>http://unitsofmeasure.org</t>
   </si>
   <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].code</t>
   </si>
   <si>
+    <t>Observation.component.value[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
     <t>mm[Hg]</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.component:systolic.dataAbsentReason</t>
@@ -1990,6 +1959,9 @@
   </si>
   <si>
     <t>Observation.component:diastolic.value[x].value</t>
+  </si>
+  <si>
+    <t>667: transform using Split_rate_value.Diastolic on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:diastolic.value[x].comparator</t>
@@ -2327,12 +2299,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR103"/>
+  <dimension ref="A1:AR95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.07421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.97265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -9922,14 +9894,16 @@
         <v>84</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>523</v>
@@ -9941,7 +9915,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9950,7 +9924,7 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>368</v>
@@ -9973,14 +9947,12 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9998,22 +9970,22 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="O61" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10041,10 +10013,10 @@
         <v>292</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -10062,7 +10034,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10071,7 +10043,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -10080,19 +10052,19 @@
         <v>84</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>529</v>
+        <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10103,21 +10075,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>534</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -10129,16 +10101,20 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>207</v>
+        <v>382</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -10162,13 +10138,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -10186,37 +10162,37 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>209</v>
+        <v>534</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10230,11 +10206,11 @@
         <v>535</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10253,18 +10229,20 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>141</v>
+        <v>536</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>213</v>
+        <v>537</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10300,19 +10278,19 @@
         <v>84</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>216</v>
+        <v>535</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10324,7 +10302,7 @@
         <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>84</v>
@@ -10333,10 +10311,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>210</v>
+        <v>446</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10353,24 +10331,26 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>84</v>
@@ -10379,19 +10359,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>539</v>
+        <v>439</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>540</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>541</v>
+        <v>507</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10440,19 +10420,19 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>544</v>
+        <v>504</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>106</v>
+        <v>511</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10461,10 +10441,10 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10473,18 +10453,18 @@
         <v>84</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>550</v>
+        <v>514</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10501,30 +10481,26 @@
         <v>84</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>551</v>
+        <v>207</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>552</v>
+        <v>208</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>553</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>554</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10544,13 +10520,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>555</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>556</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10568,7 +10544,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>557</v>
+        <v>209</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10580,7 +10556,7 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10589,10 +10565,10 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>558</v>
+        <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>559</v>
+        <v>210</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10609,21 +10585,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>561</v>
+        <v>515</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
@@ -10632,21 +10608,21 @@
         <v>84</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>562</v>
+        <v>141</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10694,19 +10670,19 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>565</v>
+        <v>216</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10715,10 +10691,10 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>567</v>
+        <v>210</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10735,43 +10711,45 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>568</v>
+        <v>543</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>569</v>
+        <v>516</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>570</v>
+        <v>451</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>572</v>
+        <v>149</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10820,19 +10798,19 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>573</v>
+        <v>453</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10841,10 +10819,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>575</v>
+        <v>137</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -10861,10 +10839,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>577</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10872,13 +10850,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>84</v>
@@ -10887,19 +10865,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>578</v>
+        <v>545</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>581</v>
+        <v>521</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10909,7 +10887,7 @@
         <v>84</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>84</v>
+        <v>546</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>84</v>
@@ -10924,13 +10902,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10948,10 +10926,10 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>582</v>
+        <v>517</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>94</v>
@@ -10966,16 +10944,16 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>566</v>
+        <v>297</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>583</v>
+        <v>298</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>84</v>
@@ -10989,10 +10967,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>584</v>
+        <v>547</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11012,22 +10990,22 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>191</v>
+        <v>548</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>585</v>
+        <v>524</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>586</v>
+        <v>525</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>587</v>
+        <v>526</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11055,10 +11033,10 @@
         <v>292</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11076,7 +11054,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11085,7 +11063,7 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>588</v>
+        <v>527</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -11094,19 +11072,19 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>137</v>
+        <v>368</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11117,21 +11095,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>589</v>
+        <v>549</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>84</v>
@@ -11143,20 +11121,16 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>382</v>
+        <v>207</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>84</v>
       </c>
@@ -11180,13 +11154,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11204,37 +11178,37 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>589</v>
+        <v>209</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>390</v>
+        <v>210</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11245,14 +11219,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>590</v>
+        <v>551</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>590</v>
+        <v>552</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11271,20 +11245,18 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>591</v>
+        <v>141</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>592</v>
+        <v>213</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11320,19 +11292,19 @@
         <v>84</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>590</v>
+        <v>216</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11344,7 +11316,7 @@
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11353,10 +11325,10 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>446</v>
+        <v>210</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11373,14 +11345,12 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>593</v>
+        <v>553</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11401,19 +11371,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>439</v>
+        <v>555</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>595</v>
+        <v>556</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>507</v>
+        <v>557</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>508</v>
+        <v>558</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>509</v>
+        <v>559</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11462,19 +11432,19 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>504</v>
+        <v>560</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>511</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11483,10 +11453,10 @@
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>512</v>
+        <v>561</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>513</v>
+        <v>562</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
@@ -11495,18 +11465,18 @@
         <v>84</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>84</v>
+        <v>563</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>84</v>
+        <v>564</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>514</v>
+        <v>566</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11523,26 +11493,30 @@
         <v>84</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>206</v>
+        <v>114</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>207</v>
+        <v>567</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>208</v>
+        <v>568</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q73" s="2"/>
+      <c r="Q73" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="R73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11562,13 +11536,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11586,7 +11560,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>209</v>
+        <v>573</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11598,7 +11572,7 @@
         <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
@@ -11607,10 +11581,10 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>84</v>
+        <v>574</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>210</v>
+        <v>575</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
@@ -11627,44 +11601,44 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>515</v>
+        <v>577</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>141</v>
+        <v>578</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
@@ -11712,19 +11686,19 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>216</v>
+        <v>581</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -11733,10 +11707,10 @@
         <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>210</v>
+        <v>583</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
@@ -11753,52 +11727,50 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>585</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>451</v>
+        <v>586</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>149</v>
+        <v>588</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>84</v>
@@ -11840,19 +11812,19 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>453</v>
+        <v>590</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>84</v>
@@ -11861,10 +11833,10 @@
         <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>137</v>
+        <v>592</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
@@ -11881,10 +11853,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>517</v>
+        <v>594</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11907,29 +11879,29 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>519</v>
+        <v>596</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>520</v>
+        <v>597</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>521</v>
+        <v>598</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>601</v>
+        <v>84</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>84</v>
@@ -11944,13 +11916,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11968,10 +11940,10 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>517</v>
+        <v>600</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>94</v>
@@ -11986,16 +11958,16 @@
         <v>84</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>297</v>
+        <v>582</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>298</v>
+        <v>601</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>84</v>
@@ -12012,7 +11984,7 @@
         <v>602</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12032,22 +12004,22 @@
         <v>84</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L77" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="O77" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12075,10 +12047,10 @@
         <v>292</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12096,7 +12068,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12105,7 +12077,7 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -12114,19 +12086,19 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>529</v>
+        <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12144,14 +12116,14 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>84</v>
@@ -12163,16 +12135,20 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>207</v>
+        <v>382</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
       </c>
@@ -12196,13 +12172,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12220,37 +12196,37 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>209</v>
+        <v>534</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12264,11 +12240,11 @@
         <v>604</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12287,18 +12263,20 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>141</v>
+        <v>536</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>213</v>
+        <v>537</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
       </c>
@@ -12334,19 +12312,19 @@
         <v>84</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>216</v>
+        <v>535</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12358,7 +12336,7 @@
         <v>84</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
@@ -12367,10 +12345,10 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>210</v>
+        <v>446</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
@@ -12390,9 +12368,11 @@
         <v>605</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="D80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12413,19 +12393,19 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>539</v>
+        <v>439</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>540</v>
+        <v>607</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>541</v>
+        <v>507</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12474,19 +12454,19 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>544</v>
+        <v>504</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>106</v>
+        <v>511</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>84</v>
@@ -12495,10 +12475,10 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>
@@ -12515,10 +12495,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>550</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12535,30 +12515,26 @@
         <v>84</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>551</v>
+        <v>207</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>552</v>
+        <v>208</v>
       </c>
       <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>553</v>
-      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q81" t="s" s="2">
-        <v>554</v>
-      </c>
+      <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
         <v>84</v>
       </c>
@@ -12578,13 +12554,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>555</v>
+        <v>84</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>556</v>
+        <v>84</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12602,7 +12578,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>557</v>
+        <v>209</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12614,7 +12590,7 @@
         <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>84</v>
@@ -12623,10 +12599,10 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>558</v>
+        <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>559</v>
+        <v>210</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>84</v>
@@ -12643,44 +12619,44 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>561</v>
+        <v>515</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>562</v>
+        <v>141</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>84</v>
       </c>
@@ -12728,19 +12704,19 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>565</v>
+        <v>216</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>84</v>
@@ -12749,10 +12725,10 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>567</v>
+        <v>210</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
@@ -12769,50 +12745,52 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>569</v>
+        <v>516</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I83" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>570</v>
+        <v>451</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O83" t="s" s="2">
-        <v>572</v>
+        <v>149</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>609</v>
+        <v>84</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>84</v>
@@ -12854,19 +12832,19 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>573</v>
+        <v>453</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>84</v>
@@ -12875,10 +12853,10 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>575</v>
+        <v>137</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>84</v>
@@ -12895,10 +12873,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>577</v>
+        <v>517</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12921,29 +12899,29 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>581</v>
+        <v>521</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>611</v>
+        <v>84</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>84</v>
+        <v>613</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>84</v>
@@ -12958,13 +12936,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -12982,10 +12960,10 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>582</v>
+        <v>517</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>94</v>
@@ -13000,16 +12978,16 @@
         <v>84</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>566</v>
+        <v>297</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>583</v>
+        <v>298</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>84</v>
@@ -13023,10 +13001,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13046,22 +13024,22 @@
         <v>84</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>191</v>
+        <v>548</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>585</v>
+        <v>524</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>586</v>
+        <v>525</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>587</v>
+        <v>526</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13089,10 +13067,10 @@
         <v>292</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>84</v>
@@ -13110,7 +13088,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13119,7 +13097,7 @@
         <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>588</v>
+        <v>527</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>106</v>
@@ -13128,19 +13106,19 @@
         <v>84</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>137</v>
+        <v>368</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13151,21 +13129,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>84</v>
@@ -13177,20 +13155,16 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>382</v>
+        <v>207</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>84</v>
       </c>
@@ -13214,13 +13188,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -13238,37 +13212,37 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>589</v>
+        <v>209</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>390</v>
+        <v>210</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13279,14 +13253,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>590</v>
+        <v>552</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13305,20 +13279,18 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>591</v>
+        <v>141</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>592</v>
+        <v>213</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>84</v>
       </c>
@@ -13354,19 +13326,19 @@
         <v>84</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>590</v>
+        <v>216</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13378,7 +13350,7 @@
         <v>84</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>84</v>
@@ -13387,10 +13359,10 @@
         <v>84</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>446</v>
+        <v>210</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
@@ -13407,14 +13379,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>84</v>
       </c>
@@ -13435,19 +13405,19 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>439</v>
+        <v>555</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>617</v>
+        <v>556</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>507</v>
+        <v>557</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>508</v>
+        <v>558</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>509</v>
+        <v>559</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13496,19 +13466,19 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>504</v>
+        <v>560</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>511</v>
+        <v>106</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>84</v>
@@ -13517,10 +13487,10 @@
         <v>84</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>512</v>
+        <v>561</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>513</v>
+        <v>562</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>84</v>
@@ -13529,18 +13499,18 @@
         <v>84</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>84</v>
+        <v>618</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>84</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>514</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13557,26 +13527,30 @@
         <v>84</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>206</v>
+        <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>207</v>
+        <v>567</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>208</v>
+        <v>568</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="R89" t="s" s="2">
         <v>84</v>
       </c>
@@ -13596,13 +13570,13 @@
         <v>84</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
@@ -13620,7 +13594,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>209</v>
+        <v>573</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13632,7 +13606,7 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>84</v>
@@ -13641,10 +13615,10 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>84</v>
+        <v>574</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>210</v>
+        <v>575</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
@@ -13661,44 +13635,44 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>515</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>141</v>
+        <v>578</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
       </c>
@@ -13746,19 +13720,19 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>216</v>
+        <v>581</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>84</v>
@@ -13767,10 +13741,10 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>210</v>
+        <v>583</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>84</v>
@@ -13787,52 +13761,50 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>516</v>
+        <v>585</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>451</v>
+        <v>586</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>149</v>
+        <v>588</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>84</v>
@@ -13874,19 +13846,19 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>453</v>
+        <v>590</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>84</v>
@@ -13895,10 +13867,10 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>137</v>
+        <v>592</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>
@@ -13915,10 +13887,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>594</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13941,29 +13913,29 @@
         <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>622</v>
+        <v>595</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>519</v>
+        <v>596</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>520</v>
+        <v>597</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>521</v>
+        <v>598</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>623</v>
+        <v>84</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>84</v>
@@ -13978,13 +13950,13 @@
         <v>84</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>84</v>
@@ -14002,10 +13974,10 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>517</v>
+        <v>600</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>94</v>
@@ -14020,16 +13992,16 @@
         <v>84</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>297</v>
+        <v>582</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>298</v>
+        <v>601</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>84</v>
@@ -14043,10 +14015,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14066,22 +14038,22 @@
         <v>84</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L93" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14109,10 +14081,10 @@
         <v>292</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14130,7 +14102,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14139,7 +14111,7 @@
         <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>106</v>
@@ -14148,19 +14120,19 @@
         <v>84</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>529</v>
+        <v>84</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14171,21 +14143,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>534</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>84</v>
@@ -14197,16 +14169,20 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>207</v>
+        <v>382</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
       </c>
@@ -14230,13 +14206,13 @@
         <v>84</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
@@ -14254,37 +14230,37 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>209</v>
+        <v>534</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14295,14 +14271,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -14321,18 +14297,20 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>141</v>
+        <v>536</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>213</v>
+        <v>537</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14368,19 +14346,19 @@
         <v>84</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>216</v>
+        <v>535</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14392,7 +14370,7 @@
         <v>84</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>84</v>
@@ -14401,10 +14379,10 @@
         <v>84</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>210</v>
+        <v>446</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>84</v>
@@ -14416,1031 +14394,11 @@
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q97" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="R97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR100" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR103" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR103">
+  <autoFilter ref="A1:AR95">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15450,7 +14408,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI102">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsObservationBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA GMRV VITAL MEASUREMENT (file 120.5) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to us-core-blood-pressure</t>
   </si>
   <si>
     <t>Purpose</t>
